--- a/employee_information_forms/027_employee_earnings_overview--employee_information_forms.xlsx
+++ b/employee_information_forms/027_employee_earnings_overview--employee_information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'employee_information_forms'}</t>
+          <t>employee_information_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Employee Information Forms'}</t>
+          <t>Employee Information Forms</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'027_employee_earnings_overview--employee_information_forms'}</t>
+          <t>027_employee_earnings_overview--employee_information_forms</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': '027_employee_earnings_overview--employee_information_forms'}</t>
+          <t>027 employee earnings overview--employee information forms</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'027_employee_earnings_overview--employee_information_forms'}</t>
+          <t>027_employee_earnings_overview--employee_information_forms</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': '027_employee_earnings_overview--employee_information_forms'}</t>
+          <t>027 employee earnings overview--employee information forms</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
